--- a/radeep_data_quality_check.xlsx
+++ b/radeep_data_quality_check.xlsx
@@ -4204,7 +4204,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r1] = '25' or [acute_id_scd_r1] = '27' or [acute_id_scd_r1] = '35' or [acute_id_scd_r1] = '42', or [acute_id_scd_r1] = '44', or [acute_id_scd_r1] = '45', or [acute_id_scd_r1] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Cannot be empty if [transfusion_status_present] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [transfusion_status_present] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Cannot be empty if [regular_transfusion_type] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [regular_transfusion_type] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Cannot be empty if [chelation_treat] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [chelation_treat] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [hydroxiurea_treatment] = '1' / If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If not empty, branching must be [hydroxiurea_treatment] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Cannot be empty if [transplanted] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [transplanted] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10675,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>test_result_53</t>
+          <t>test_result_31</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Blood film morphology</t>
+          <t>Pyruvate kinase</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10695,45 +10695,37 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>[test_performed_53] = '1'</t>
+          <t>[test_performed_31] = '1'</t>
         </is>
       </c>
       <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Cannot be empty if blood film morphology test is performed.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>(([test_result_53(1)]=0 AND [test_result_53(2)]=0 AND [test_result_53(3)]=0 AND [test_result_53(4)]=0 AND [test_result_53(5)]=0 AND [test_result_53(6)]=0 AND [test_result_53(7)]=0 AND [test_result_53(8)]=0 AND [test_result_53(9)]=0 AND [test_result_53(10)]=0 AND [test_result_53(11)]=0 AND [test_result_53(12)]=0 AND [test_result_53(13)]=0 AND [test_result_53(14)]=0 AND [test_result_53(15)]=0 AND [test_result_53(16)]=0 AND [test_result_53(17)]=0 AND [test_result_53(18)]=0 AND [test_result_53(19)]=0 AND [test_result_53(20)]=0 AND [test_result_53(21)]=0) AND ([diagnosis_complete]=2)) AND ([test_performed_53] = '1')</t>
-        </is>
-      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_53] = '1'</t>
+          <t>Cannot be empty if [test_performed_31] = '1'</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>test_result_62</t>
+          <t>test_result_32</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neutrophils result </t>
+          <t>Hexokinase</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10743,49 +10735,37 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>[test_performed_62] = '1'</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Cannot be empty if neutrophils test is performed.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>(([test_result_62]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_62] = '1')</t>
-        </is>
-      </c>
+          <t>[test_performed_32] = '1'</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_62] = '1'</t>
+          <t>Cannot be empty if [test_performed_32] = '1'</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>test_result_63</t>
+          <t>test_result_33</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Lymphocytes result</t>
+          <t>Glucose-6-phosphate dehydrogenase</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10795,49 +10775,37 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>[test_performed_63] = '1'</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Cannot be empty if lymphocytes test is performed.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>(([test_result_63]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_63] = '1')</t>
-        </is>
-      </c>
+          <t>[test_performed_33] = '1'</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_63] = '1'</t>
+          <t>Cannot be empty if [test_performed_33] = '1'</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>test_result_64</t>
+          <t>test_result_34</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Monocytes result</t>
+          <t>Glucose Phosphate isomerase</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10847,49 +10815,37 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>[test_performed_64] = '1'</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Cannot be empty if monocytes test is performed.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>(([test_result_64]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_64] = '1')</t>
-        </is>
-      </c>
+          <t>[test_performed_34] = '1'</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_64] = '1'</t>
+          <t>Cannot be empty if [test_performed_34] = '1'</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>test_result_65</t>
+          <t>test_result_35</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Eosinophils result</t>
+          <t>Adenosine deaminase</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10899,49 +10855,37 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>[test_performed_65] = '1'</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Cannot be empty if eosinophils test is performed.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>(([test_result_65]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_65] = '1')</t>
-        </is>
-      </c>
+          <t>[test_performed_35] = '1'</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_65] = '1'</t>
+          <t>Cannot be empty if [test_performed_35] = '1'</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>test_result_66</t>
+          <t>test_result_36</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Basophils result</t>
+          <t>Adenylate kinase</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -10951,49 +10895,37 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>[test_performed_66] = '1'</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Cannot be empty if basophils test is performed.</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>(([test_result_66]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_66] = '1')</t>
-        </is>
-      </c>
+          <t>[test_performed_36] = '1'</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_66] = '1'</t>
+          <t>Cannot be empty if [test_performed_36] = '1'</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>test_result_69</t>
+          <t>test_result_37</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Total iron binding capacity result</t>
+          <t>Aldolase</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11003,116 +10935,132 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>[test_performed_69] = '1'</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Cannot be empty if total iron binding capacity test is performed. Value range should be higher than 0 and lower than 1000. Alert shown if value is lower than 0 or higher than 1000.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>(([test_result_69]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_69] = '1')</t>
-        </is>
-      </c>
+          <t>[test_performed_37] = '1'</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_69] = '1' / Value range should be higher than 0 and lower than 1000 / Alert shown if lower than 0 or higher than 1000</t>
+          <t>Cannot be empty if [test_performed_37] = '1'</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>record_id</t>
+          <t>test_result_38</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Record ID</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Bisphosphoglycerate mutase</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr"/>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>[test_performed_38] = '1'</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_38] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>calc_val</t>
+          <t>test_result_39</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Pseudonym validation</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>NADH-cytochrome b5 reductase</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>calc</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr"/>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>[test_performed_39] = '1'</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_39] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>alert_val_id</t>
+          <t>test_result_40</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>&lt;div class='alert alert-danger'&gt;There is a mistake in the format of the pseudonym. Please check the values.&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>g-Glutamylcysteine synthetase</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>[calc_val]='2'</t>
+          <t>[test_performed_40] = '1'</t>
         </is>
       </c>
       <c r="G236" t="inlineStr"/>
@@ -11120,48 +11068,64 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [calc_val]='2'</t>
+          <t>Cannot be empty if [test_performed_40] = '1'</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>test_result_41</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>patient_registration</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
+          <t>diagnosis</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Gluthathione reductase</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>calc</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr"/>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>[test_performed_41] = '1'</t>
+        </is>
+      </c>
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_41] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>death_cause_other</t>
+          <t>test_result_42</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Other cause of death</t>
+          <t>Glutathione synthetase</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11171,12 +11135,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>[cause_of_death] = '998'</t>
+          <t>[test_performed_42] = '1'</t>
         </is>
       </c>
       <c r="G238" t="inlineStr"/>
@@ -11184,24 +11148,24 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Cannot be empty if [cause_of_death] = '998'</t>
+          <t>Cannot be empty if [test_performed_42] = '1'</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>date_hcp_contact</t>
+          <t>test_result_43</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Date of first contact with HCP</t>
+          <t>Phosphofructokinase</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11211,113 +11175,117 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>[first_hcp_contact] = '1'</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>date_dmy</t>
-        </is>
-      </c>
+          <t>[test_performed_43] = '1'</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>[date_hcp_contact]='' and [patient_registration_complete]='2' and ([first_hcp_contact] = '1')</t>
-        </is>
-      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Cannot be empty if [first_hcp_contact] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [test_performed_43] = '1'</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>test_result_44</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Date of event registration</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>Phosphoglycerate kinase</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>datetime_seconds_ymd</t>
-        </is>
-      </c>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>[test_performed_44] = '1'</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_44] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>calc_year_of_immigration</t>
+          <t>test_result_45</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Calc year of immigration</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>Pyrimidine-5'-nucleotidase</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>date_dmy</t>
-        </is>
-      </c>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>[test_performed_45] = '1'</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [test_performed_45] = '1'</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>comorbidities_other</t>
+          <t>test_result_46</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Comorbidities other</t>
+          <t>Triosephosphate isomerase</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11327,12 +11295,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>[comorbiditiesid(998)] = '1'</t>
+          <t>[test_performed_46] = '1'</t>
         </is>
       </c>
       <c r="G242" t="inlineStr"/>
@@ -11340,24 +11308,24 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Cannot be empty if [comorbiditiesid(998)] = '1'</t>
+          <t>Cannot be empty if [test_performed_46] = '1'</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>cm_unknown</t>
+          <t>test_result_47</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Eosin-5-maleimide (EMA) binding test</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11372,36 +11340,32 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>[patient_registrati_arm_1][patient_status] = '1'</t>
+          <t>[test_performed_47] = '1'</t>
         </is>
       </c>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>[cm_unknown]='' and [annual_update_general_information_complete]='2'</t>
-        </is>
-      </c>
+      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Cannot be empty if [patient_registrati_arm_1][patient_status] = '1'</t>
+          <t>Cannot be empty if [test_performed_47] = '1'</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kg_unknown</t>
+          <t>test_result_48</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weight </t>
+          <t>Ektacytometry</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11416,54 +11380,62 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>[patient_registrati_arm_1][patient_status] = '1'</t>
+          <t>[test_performed_48] = '1'</t>
         </is>
       </c>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>[kg_unknown]='' and [annual_update_general_information_complete]='2'</t>
-        </is>
-      </c>
+      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Cannot be empty if [patient_registrati_arm_1][patient_status] = '1'</t>
+          <t>Cannot be empty if [test_performed_48] = '1'</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>timestamp_label</t>
+          <t>test_result_49</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
+          <t>diagnosis</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sodium dodecyl sulfate-polyacrylamide gel electrophoresis (SDS-PAGE) </t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>date_ymd</t>
-        </is>
-      </c>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>[test_performed_49] = '1'</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_49] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>enter_clin_diag_date</t>
+          <t>test_result_50</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -11473,7 +11445,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Date of clinical diagnosis:</t>
+          <t>Osmotic Fragility Test or glycerol lysis test</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11483,35 +11455,27 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>[age_date_at_diagnosis] = '4'</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>date_dmy</t>
-        </is>
-      </c>
+          <t>[test_performed_50] = '1'</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>(([enter_clin_diag_date]='') AND ([diagnosis_complete]=2)) AND ([age_date_at_diagnosis] = '4')</t>
-        </is>
-      </c>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Cannot be empty if [age_date_at_diagnosis] = '4' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [test_performed_50] = '1'</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>undiagnosed_other_text</t>
+          <t>test_result_51</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -11521,7 +11485,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Undiagnosed other, specify</t>
+          <t>Hepcidin</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11531,12 +11495,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_undiagnosed] = '998'</t>
+          <t>[test_performed_51] = '1'</t>
         </is>
       </c>
       <c r="G247" t="inlineStr"/>
@@ -11544,14 +11508,14 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_undiagnosed] = '998'</t>
+          <t>Cannot be empty if [test_performed_51] = '1'</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sub_orpha_id_other</t>
+          <t>test_result_52</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -11561,7 +11525,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Sub-diagnosis</t>
+          <t>Bone marrow examination</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11571,35 +11535,27 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>checkbox</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '998'</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>autocomplete</t>
-        </is>
-      </c>
+          <t>[test_performed_52] = '1'</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>(([sub_orpha_id_other]='') AND ([diagnosis_complete]=2)) AND ([orpha_code_id] = '998')</t>
-        </is>
-      </c>
+      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '998'</t>
+          <t>Cannot be empty if [test_performed_52] = '1'</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>hpo_row_2</t>
+          <t>test_result_53</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -11607,296 +11563,436 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Blood film morphology</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>checkbox</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>[test_performed_53] = '1'</t>
+        </is>
+      </c>
       <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Cannot be empty if blood film morphology test is performed.</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>(([test_result_53(1)]=0 AND [test_result_53(2)]=0 AND [test_result_53(3)]=0 AND [test_result_53(4)]=0 AND [test_result_53(5)]=0 AND [test_result_53(6)]=0 AND [test_result_53(7)]=0 AND [test_result_53(8)]=0 AND [test_result_53(9)]=0 AND [test_result_53(10)]=0 AND [test_result_53(11)]=0 AND [test_result_53(12)]=0 AND [test_result_53(13)]=0 AND [test_result_53(14)]=0 AND [test_result_53(15)]=0 AND [test_result_53(16)]=0 AND [test_result_53(17)]=0 AND [test_result_53(18)]=0 AND [test_result_53(19)]=0 AND [test_result_53(20)]=0 AND [test_result_53(21)]=0) AND ([diagnosis_complete]=2)) AND ([test_performed_53] = '1')</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_53] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>hpo_row_3</t>
+          <t>test_result_62</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
+          <t>laboratory_tests</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neutrophils result </t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>[test_performed_62] = '1'</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Cannot be empty if neutrophils test is performed.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>(([test_result_62]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_62] = '1')</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_62] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>hpo_row_4</t>
+          <t>test_result_63</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
+          <t>laboratory_tests</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Lymphocytes result</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>[test_performed_63] = '1'</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Cannot be empty if lymphocytes test is performed.</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>(([test_result_63]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_63] = '1')</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_63] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>hpo_row_5</t>
+          <t>test_result_64</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
+          <t>laboratory_tests</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Monocytes result</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>[test_performed_64] = '1'</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Cannot be empty if monocytes test is performed.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>(([test_result_64]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_64] = '1')</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_64] = '1'</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>hpoid_table_1</t>
+          <t>test_result_65</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>laboratory_tests</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_1}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>Eosinophils result</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '16'</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
+          <t>[test_performed_65] = '1'</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Cannot be empty if eosinophils test is performed.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>(([test_result_65]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_65] = '1')</t>
+        </is>
+      </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16'</t>
+          <t>Cannot be empty if [test_performed_65] = '1'</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>hpoid_table_2</t>
+          <t>test_result_66</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>laboratory_tests</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_2}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_3}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>Basophils result</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '16' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
+          <t>[test_performed_66] = '1'</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Cannot be empty if basophils test is performed.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>(([test_result_66]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_66] = '1')</t>
+        </is>
+      </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_2(1)] = '1'</t>
+          <t>Cannot be empty if [test_performed_66] = '1'</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>hpoid_table_3</t>
+          <t>test_result_69</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>laboratory_tests</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_3}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_4}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Total iron binding capacity result</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '16' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
+          <t>[test_performed_69] = '1'</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Cannot be empty if total iron binding capacity test is performed. Value range should be higher than 0 and lower than 1000. Alert shown if value is lower than 0 or higher than 1000.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>(([test_result_69]='') AND ([laboratory_tests_complete]=2)) AND ([test_performed_69] = '1')</t>
+        </is>
+      </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
+          <t>Cannot be empty if [test_performed_69] = '1' / Value range should be higher than 0 and lower than 1000 / Alert shown if lower than 0 or higher than 1000</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>hpoid_table_4</t>
+          <t>record_id</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_4}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Record ID</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>descriptive</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>[orpha_code_id] = '16' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
+      <c r="J256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>hpoid_table_5</t>
+          <t>calc_val</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 100%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 100%; text-align: center; height: 18px;"&gt;{hpoid_5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Pseudonym validation</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>descriptive</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>[orpha_code_id] = '16' and [hpo_row_5(1)] = '1' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
+          <t>calc</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_5(1)] = '1' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
+      <c r="J257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>new_variation_pklr_a1</t>
+          <t>alert_val_id</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Novel variation PKLR Allele 1</t>
+          <t>&lt;div class='alert alert-danger'&gt;There is a mistake in the format of the pseudonym. Please check the values.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>[varsid_pklr_a1] = '3150' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[calc_val]='2'</t>
         </is>
       </c>
       <c r="G258" t="inlineStr"/>
@@ -11904,63 +12000,55 @@
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_pklr_a1] = '3150' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [calc_val]='2'</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>new_variation_pklr_a2</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Novel variation PKLR Allele 2</t>
-        </is>
-      </c>
+          <t>patient_registration</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>[varsid_pklr_a2] = '3150' and [method_of_diagnosis(3)] = '1'</t>
-        </is>
-      </c>
+          <t>calc</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_pklr_a2] = '3150' and [method_of_diagnosis(3)] = '1'</t>
-        </is>
-      </c>
+      <c r="J259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>new_variation_hbb_a1</t>
+          <t>death_cause_other</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Novel variation HBB Allele 1</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
+          <t>Other cause of death</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>text</t>
@@ -11968,7 +12056,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>[varsid_hbb_a1] = '3150'</t>
+          <t>[cause_of_death] = '998'</t>
         </is>
       </c>
       <c r="G260" t="inlineStr"/>
@@ -11976,27 +12064,31 @@
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbb_a1] = '3150'</t>
+          <t>Cannot be empty if [cause_of_death] = '998'</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>new_variation_hbb_a2</t>
+          <t>date_hcp_contact</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Novel variation HBB Allele 2</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Date of first contact with HCP</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>text</t>
@@ -12004,32 +12096,40 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>[varsid_hbb_a2] = '3150'</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr"/>
+          <t>[first_hcp_contact] = '1'</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>date_dmy</t>
+        </is>
+      </c>
       <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>[date_hcp_contact]='' and [patient_registration_complete]='2' and ([first_hcp_contact] = '1')</t>
+        </is>
+      </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbb_a2] = '3150'</t>
+          <t>Cannot be empty if [first_hcp_contact] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>new_variation_hba1_a1</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Novel variation HBA1 Allele 1</t>
+          <t>Date of event registration</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -12038,34 +12138,30 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>[varsid_hba1_a1] = '3150'</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>datetime_seconds_ymd</t>
+        </is>
+      </c>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hba1_a1] = '3150'</t>
-        </is>
-      </c>
+      <c r="J262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>new_variation_hba1_a2</t>
+          <t>calc_year_of_immigration</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Novel variation HBA1 Allele 2</t>
+          <t>Calc year of immigration</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -12074,37 +12170,41 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>[varsid_hba2_a2] = '3150'</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>date_dmy</t>
+        </is>
+      </c>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hba2_a2] = '3150'</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>new_variation_hba2_a1</t>
+          <t>comorbidities_other</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Novel variation HBA2 Allele 1</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>Comorbidities other</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>text</t>
@@ -12112,7 +12212,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>[varsid_hba2_a1] = '3150'</t>
+          <t>[comorbiditiesid(998)] = '1'</t>
         </is>
       </c>
       <c r="G264" t="inlineStr"/>
@@ -12120,122 +12220,130 @@
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hba2_a1] = '3150'</t>
+          <t>Cannot be empty if [comorbiditiesid(998)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>new_variation_hba2_a2</t>
+          <t>cm_unknown</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Novel variation HBA2 Allele 2</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr"/>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>[varsid_hba2_a2] = '3150'</t>
+          <t>[patient_registrati_arm_1][patient_status] = '1'</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>[cm_unknown]='' and [annual_update_general_information_complete]='2'</t>
+        </is>
+      </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hba2_a2] = '3150'</t>
+          <t>Cannot be empty if [patient_registrati_arm_1][patient_status] = '1'</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>new_variation_hbbp1_a1</t>
+          <t>kg_unknown</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Novel variation HBBP1 Allele 1</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
+          <t xml:space="preserve">Weight </t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>[varsid_hbbp1_a1] = '3150'</t>
+          <t>[patient_registrati_arm_1][patient_status] = '1'</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>[kg_unknown]='' and [annual_update_general_information_complete]='2'</t>
+        </is>
+      </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbbp1_a1] = '3150'</t>
+          <t>Cannot be empty if [patient_registrati_arm_1][patient_status] = '1'</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>new_variation_hbbp1_a2</t>
+          <t>timestamp_label</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Novel variation HBBP1 Allele 2</t>
-        </is>
-      </c>
+          <t>annual_update_general_information</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>[varsid_hbbp1_a2] = '3150'</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>date_ymd</t>
+        </is>
+      </c>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbbp1_a2] = '3150'</t>
-        </is>
-      </c>
+      <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>new_variation_hbd_a1</t>
+          <t>enter_clin_diag_date</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -12245,10 +12353,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Novel variation HBD Allele 1</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>Date of clinical diagnosis:</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>text</t>
@@ -12256,22 +12368,30 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>[varsid_hbd_a1] = '3150'</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr"/>
+          <t>[age_date_at_diagnosis] = '4'</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>date_dmy</t>
+        </is>
+      </c>
       <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>(([enter_clin_diag_date]='') AND ([diagnosis_complete]=2)) AND ([age_date_at_diagnosis] = '4')</t>
+        </is>
+      </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbd_a1] = '3150'</t>
+          <t>Cannot be empty if [age_date_at_diagnosis] = '4' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>new_variation_hbd_a2</t>
+          <t>undiagnosed_other_text</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12281,10 +12401,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Novel variation HBD Allele 2</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Undiagnosed other, specify</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>text</t>
@@ -12292,7 +12416,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>[varsid_hbd_a2] = '3150'</t>
+          <t>[sub_orpha_id_undiagnosed] = '998'</t>
         </is>
       </c>
       <c r="G269" t="inlineStr"/>
@@ -12300,14 +12424,14 @@
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbd_a2] = '3150'</t>
+          <t>Cannot be empty if [sub_orpha_id_undiagnosed] = '998'</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>new_variation_hbe1_a1</t>
+          <t>sub_orpha_id_other</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -12317,33 +12441,45 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Novel variation HBE1 Allele 1</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Sub-diagnosis</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>[varsid_hbe1_a1] = '3150'</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr"/>
+          <t>[orpha_code_id] = '998'</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>autocomplete</t>
+        </is>
+      </c>
       <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>(([sub_orpha_id_other]='') AND ([diagnosis_complete]=2)) AND ([orpha_code_id] = '998')</t>
+        </is>
+      </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbe1_a1] = '3150'</t>
+          <t>Cannot be empty if [orpha_code_id] = '998'</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>new_variation_hbe1_a2</t>
+          <t>hpo_row_2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12351,35 +12487,23 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Novel variation HBE1 Allele 2</t>
-        </is>
-      </c>
+      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>[varsid_hbe1_a2] = '3150'</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbe1_a2] = '3150'</t>
-        </is>
-      </c>
+      <c r="J271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>new_variation_hbg1_a1</t>
+          <t>hpo_row_3</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -12387,35 +12511,23 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Novel variation HBG1 Allele 1</t>
-        </is>
-      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>[varsid_hbg1_a1] = '3150'</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbg1_a1] = '3150'</t>
-        </is>
-      </c>
+      <c r="J272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>new_variation_hbg1_a2</t>
+          <t>hpo_row_4</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12423,35 +12535,23 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Novel variation HBG1 Allele 2</t>
-        </is>
-      </c>
+      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>[varsid_hbg1_a2] = '3150'</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbg1_a2] = '3150'</t>
-        </is>
-      </c>
+      <c r="J273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>new_variation_hbg2_a1</t>
+          <t>hpo_row_5</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -12459,35 +12559,23 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Novel variation HBG2 Allele 1</t>
-        </is>
-      </c>
+      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>[varsid_hbg2_a1] = '3150'</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbg2_a1] = '3150'</t>
-        </is>
-      </c>
+      <c r="J274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>new_variation_hbg2_a2</t>
+          <t>hpoid_table_1</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12497,18 +12585,18 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Novel variation HBG2 Allele 2</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_1}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>[varsid_hbg2_a2] = '3150'</t>
+          <t>[orpha_code_id] = '16'</t>
         </is>
       </c>
       <c r="G275" t="inlineStr"/>
@@ -12516,14 +12604,14 @@
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbg2_a2] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16'</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>new_variation_hbm_a1</t>
+          <t>hpoid_table_2</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -12533,18 +12621,18 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Novel variation HBM Allele 1</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_2}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_3}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>[varsid_hbm_a1] = '3150'</t>
+          <t>[orpha_code_id] = '16' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="G276" t="inlineStr"/>
@@ -12552,14 +12640,14 @@
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbm_a1] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>new_variation_hbm_a2</t>
+          <t>hpoid_table_3</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12569,18 +12657,18 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Novel variation HBM Allele 2</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_3}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_4}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>[varsid_hbm_a1] = '3150'</t>
+          <t>[orpha_code_id] = '16' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="G277" t="inlineStr"/>
@@ -12588,14 +12676,14 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbm_a1] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>new_variation_hbz_a1</t>
+          <t>hpoid_table_4</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -12605,18 +12693,18 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Novel variation HBZ Allele 1</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_4}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>[varsid_hbz_a1] = '3150'</t>
+          <t>[orpha_code_id] = '16' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="G278" t="inlineStr"/>
@@ -12624,14 +12712,14 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbz_a1] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>new_variation_hbz_a2</t>
+          <t>hpoid_table_5</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12641,18 +12729,18 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Novel variation HBZ Allele 2</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 100%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 100%; text-align: center; height: 18px;"&gt;{hpoid_5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>[varsid_hbz_a2] = '3150'</t>
+          <t>[orpha_code_id] = '16' and [hpo_row_5(1)] = '1' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="G279" t="inlineStr"/>
@@ -12660,14 +12748,14 @@
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbz_a2] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_5(1)] = '1' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>new_variation_hs40_a1</t>
+          <t>new_variation_pklr_a1</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -12677,7 +12765,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Novel variation HS40 Allele 1</t>
+          <t>Novel variation PKLR Allele 1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -12688,7 +12776,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>[varsid_hs40_a1] = '3150'</t>
+          <t>[varsid_pklr_a1] = '3150' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G280" t="inlineStr"/>
@@ -12696,14 +12784,14 @@
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hs40_a1] = '3150'</t>
+          <t>If not empty, branching must be [varsid_pklr_a1] = '3150' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>new_variation_hs40_a2</t>
+          <t>new_variation_pklr_a2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12713,7 +12801,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Novel variation HS40 Allele 2</t>
+          <t>Novel variation PKLR Allele 2</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -12724,7 +12812,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>[varsid_hs40_a2] = '3150'</t>
+          <t>[varsid_pklr_a2] = '3150' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G281" t="inlineStr"/>
@@ -12732,14 +12820,14 @@
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hs40_a2] = '3150'</t>
+          <t>If not empty, branching must be [varsid_pklr_a2] = '3150' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>new_variation_lcrb_a1</t>
+          <t>new_variation_hbb_a1</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -12749,7 +12837,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Novel variation LCRB Allele 1</t>
+          <t>Novel variation HBB Allele 1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -12760,7 +12848,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>[varsid_lcrb_a1] = '3150'</t>
+          <t>[varsid_hbb_a1] = '3150'</t>
         </is>
       </c>
       <c r="G282" t="inlineStr"/>
@@ -12768,14 +12856,14 @@
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_lcrb_a1] = '3150'</t>
+          <t>If not empty, branching must be [varsid_hbb_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>new_variation_lcrb_a2</t>
+          <t>new_variation_hbb_a2</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12785,7 +12873,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Novel variation LCRB Allele 2</t>
+          <t>Novel variation HBB Allele 2</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -12796,7 +12884,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>[varsid_lcrb_a1] = '3150'</t>
+          <t>[varsid_hbb_a2] = '3150'</t>
         </is>
       </c>
       <c r="G283" t="inlineStr"/>
@@ -12804,14 +12892,14 @@
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_lcrb_a1] = '3150'</t>
+          <t>If not empty, branching must be [varsid_hbb_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>new_variation_a3_7hybrid_a1</t>
+          <t>new_variation_hba1_a1</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -12821,7 +12909,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Novel variation A3.7 Hybrid Allele 1</t>
+          <t>Novel variation HBA1 Allele 1</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -12832,7 +12920,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>[varsid_a3_7hybrid_a1] = '3150'</t>
+          <t>[varsid_hba1_a1] = '3150'</t>
         </is>
       </c>
       <c r="G284" t="inlineStr"/>
@@ -12840,14 +12928,14 @@
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_a3_7hybrid_a1] = '3150'</t>
+          <t>If not empty, branching must be [varsid_hba1_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>new_variation_a3_7hybrid_a2</t>
+          <t>new_variation_hba1_a2</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12857,7 +12945,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Novel variation A3.7 Hybrid Allele 2</t>
+          <t>Novel variation HBA1 Allele 2</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -12868,7 +12956,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>[varsid_a3_7hybrid_a2] = '3150'</t>
+          <t>[varsid_hba2_a2] = '3150'</t>
         </is>
       </c>
       <c r="G285" t="inlineStr"/>
@@ -12876,14 +12964,14 @@
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_a3_7hybrid_a2] = '3150'</t>
+          <t>If not empty, branching must be [varsid_hba2_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>gene_table</t>
+          <t>new_variation_hba2_a1</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -12893,18 +12981,18 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100.141%; height: 290.188px;" border="1"&gt; &lt;thead&gt; &lt;tr style="height: 38.1875px; background-color: #95a5a6;"&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt;Gene&lt;/td&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt; &lt;p style="text-align: center;"&gt;Allele 2&lt;/p&gt; &lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;PKLR&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_pklr_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_pklr_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;HBB&lt;/td&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;{varsid_hbb_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;{varsid_hbb_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBA1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBA2&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba2_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba2_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBBP1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbbp1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbbp1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBD&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbd_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbd_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBE1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbe1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbe1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBG1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBG2&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg2_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg2_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBM&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbm_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbm_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBZ&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbz_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbz_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HS40&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hs40_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hs40_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;LCRB&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_lcrb_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_lcrb_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;A3.7 Hybrid&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_a3_7hybrid_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_a3_7hybrid_a2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation HBA2 Allele 1</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>[gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hba2_a1] = '3150'</t>
         </is>
       </c>
       <c r="G286" t="inlineStr"/>
@@ -12912,14 +13000,14 @@
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hba2_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>gene_type_novel</t>
+          <t>new_variation_hba2_a2</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12929,22 +13017,18 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Novel Gene</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Novel variation HBA2 Allele 2</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>yesno</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>[gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hba2_a2] = '3150'</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
@@ -12952,14 +13036,14 @@
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Cannot be empty if [gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hba2_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>novelsymbol_r1</t>
+          <t>new_variation_hbbp1_a1</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -12967,7 +13051,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Novel variation HBBP1 Allele 1</t>
+        </is>
+      </c>
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
@@ -12976,7 +13064,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>[gene_type_novel] = '1'</t>
+          <t>[varsid_hbbp1_a1] = '3150'</t>
         </is>
       </c>
       <c r="G288" t="inlineStr"/>
@@ -12984,14 +13072,14 @@
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbbp1_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>var_allele2_r1</t>
+          <t>new_variation_hbbp1_a2</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12999,7 +13087,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Novel variation HBBP1 Allele 2</t>
+        </is>
+      </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
@@ -13008,7 +13100,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>[gene_type_novel] = '1'</t>
+          <t>[varsid_hbbp1_a2] = '3150'</t>
         </is>
       </c>
       <c r="G289" t="inlineStr"/>
@@ -13016,14 +13108,14 @@
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbbp1_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>var_allele1_r1</t>
+          <t>new_variation_hbd_a1</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13031,7 +13123,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Novel variation HBD Allele 1</t>
+        </is>
+      </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
@@ -13040,7 +13136,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>[gene_type_novel] = '1'</t>
+          <t>[varsid_hbd_a1] = '3150'</t>
         </is>
       </c>
       <c r="G290" t="inlineStr"/>
@@ -13048,14 +13144,14 @@
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbd_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>new_novel_row2</t>
+          <t>new_variation_hbd_a2</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13063,23 +13159,35 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Novel variation HBD Allele 2</t>
+        </is>
+      </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>[varsid_hbd_a2] = '3150'</t>
+        </is>
+      </c>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>If not empty, branching must be [varsid_hbd_a2] = '3150'</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>novel_gene_r1</t>
+          <t>new_variation_hbe1_a1</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13089,18 +13197,18 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; Add new row&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r1}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r1}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r1}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation HBE1 Allele 1</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>[gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hbe1_a1] = '3150'</t>
         </is>
       </c>
       <c r="G292" t="inlineStr"/>
@@ -13108,14 +13216,14 @@
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbe1_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>var_allele2_r2</t>
+          <t>new_variation_hbe1_a2</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13123,7 +13231,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Novel variation HBE1 Allele 2</t>
+        </is>
+      </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
@@ -13132,7 +13244,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hbe1_a2] = '3150'</t>
         </is>
       </c>
       <c r="G293" t="inlineStr"/>
@@ -13140,14 +13252,14 @@
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbe1_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>novelsymbol_r2</t>
+          <t>new_variation_hbg1_a1</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13155,7 +13267,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Novel variation HBG1 Allele 1</t>
+        </is>
+      </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
@@ -13164,7 +13280,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hbg1_a1] = '3150'</t>
         </is>
       </c>
       <c r="G294" t="inlineStr"/>
@@ -13172,14 +13288,14 @@
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbg1_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>var_allele1_r2</t>
+          <t>new_variation_hbg1_a2</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13187,7 +13303,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Novel variation HBG1 Allele 2</t>
+        </is>
+      </c>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
@@ -13196,7 +13316,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hbg1_a2] = '3150'</t>
         </is>
       </c>
       <c r="G295" t="inlineStr"/>
@@ -13204,14 +13324,14 @@
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbg1_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>new_novel_row3</t>
+          <t>new_variation_hbg2_a1</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13219,23 +13339,35 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Novel variation HBG2 Allele 1</t>
+        </is>
+      </c>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>[varsid_hbg2_a1] = '3150'</t>
+        </is>
+      </c>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>If not empty, branching must be [varsid_hbg2_a1] = '3150'</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>novel_gene_r2</t>
+          <t>new_variation_hbg2_a2</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13245,18 +13377,18 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r2}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r2}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r2}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row3}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation HBG2 Allele 2</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hbg2_a2] = '3150'</t>
         </is>
       </c>
       <c r="G297" t="inlineStr"/>
@@ -13264,14 +13396,14 @@
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbg2_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>new_novel_row4</t>
+          <t>new_variation_hbm_a1</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13279,23 +13411,35 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Novel variation HBM Allele 1</t>
+        </is>
+      </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>[varsid_hbm_a1] = '3150'</t>
+        </is>
+      </c>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>If not empty, branching must be [varsid_hbm_a1] = '3150'</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>novelsymbol_r3</t>
+          <t>new_variation_hbm_a2</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13303,7 +13447,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Novel variation HBM Allele 2</t>
+        </is>
+      </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
@@ -13312,7 +13460,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hbm_a1] = '3150'</t>
         </is>
       </c>
       <c r="G299" t="inlineStr"/>
@@ -13320,14 +13468,14 @@
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbm_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>var_allele1_r3</t>
+          <t>new_variation_hbz_a1</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13335,7 +13483,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Novel variation HBZ Allele 1</t>
+        </is>
+      </c>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
@@ -13344,7 +13496,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hbz_a1] = '3150'</t>
         </is>
       </c>
       <c r="G300" t="inlineStr"/>
@@ -13352,14 +13504,14 @@
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbz_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>var_allele2_r3</t>
+          <t>new_variation_hbz_a2</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13367,7 +13519,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Novel variation HBZ Allele 2</t>
+        </is>
+      </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
@@ -13376,7 +13532,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hbz_a2] = '3150'</t>
         </is>
       </c>
       <c r="G301" t="inlineStr"/>
@@ -13384,14 +13540,14 @@
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbz_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>novel_gene_r3</t>
+          <t>new_variation_hs40_a1</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13401,18 +13557,18 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r3}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r3}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r3}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row4}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation HS40 Allele 1</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hs40_a1] = '3150'</t>
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
@@ -13420,14 +13576,14 @@
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hs40_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>var_allele1_r4</t>
+          <t>new_variation_hs40_a2</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13435,7 +13591,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Novel variation HS40 Allele 2</t>
+        </is>
+      </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
@@ -13444,7 +13604,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hs40_a2] = '3150'</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
@@ -13452,14 +13612,14 @@
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hs40_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>var_allele2_r4</t>
+          <t>new_variation_lcrb_a1</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13467,7 +13627,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Novel variation LCRB Allele 1</t>
+        </is>
+      </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
@@ -13476,7 +13640,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_lcrb_a1] = '3150'</t>
         </is>
       </c>
       <c r="G304" t="inlineStr"/>
@@ -13484,14 +13648,14 @@
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_lcrb_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>novelsymbol_r4</t>
+          <t>new_variation_lcrb_a2</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13499,7 +13663,11 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Novel variation LCRB Allele 2</t>
+        </is>
+      </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
@@ -13508,7 +13676,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_lcrb_a1] = '3150'</t>
         </is>
       </c>
       <c r="G305" t="inlineStr"/>
@@ -13516,14 +13684,14 @@
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_lcrb_a1] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>new_novel_row5</t>
+          <t>new_variation_a3_7hybrid_a1</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13531,23 +13699,35 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr"/>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Novel variation A3.7 Hybrid Allele 1</t>
+        </is>
+      </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>[varsid_a3_7hybrid_a1] = '3150'</t>
+        </is>
+      </c>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr"/>
-      <c r="J306" t="inlineStr"/>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>If not empty, branching must be [varsid_a3_7hybrid_a1] = '3150'</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>novel_gene_r4</t>
+          <t>new_variation_a3_7hybrid_a2</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13557,18 +13737,18 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r4}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r4}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r4}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation A3.7 Hybrid Allele 2</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_a3_7hybrid_a2] = '3150'</t>
         </is>
       </c>
       <c r="G307" t="inlineStr"/>
@@ -13576,14 +13756,14 @@
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_a3_7hybrid_a2] = '3150'</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>var_allele1_r5</t>
+          <t>gene_table</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13591,16 +13771,20 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100.141%; height: 290.188px;" border="1"&gt; &lt;thead&gt; &lt;tr style="height: 38.1875px; background-color: #95a5a6;"&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt;Gene&lt;/td&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt; &lt;p style="text-align: center;"&gt;Allele 2&lt;/p&gt; &lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;PKLR&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_pklr_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_pklr_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;HBB&lt;/td&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;{varsid_hbb_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;{varsid_hbb_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBA1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBA2&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba2_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba2_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBBP1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbbp1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbbp1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBD&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbd_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbd_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBE1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbe1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbe1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBG1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBG2&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg2_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg2_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBM&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbm_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbm_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBZ&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbz_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbz_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HS40&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hs40_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hs40_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;LCRB&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_lcrb_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_lcrb_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;A3.7 Hybrid&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_a3_7hybrid_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_a3_7hybrid_a2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G308" t="inlineStr"/>
@@ -13608,14 +13792,14 @@
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>var_allele2_r5</t>
+          <t>gene_type_novel</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13623,16 +13807,24 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
-      <c r="D309" t="inlineStr"/>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Novel Gene</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>yesno</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
@@ -13640,14 +13832,14 @@
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>Cannot be empty if [gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>novelsymbol_r5</t>
+          <t>novelsymbol_r1</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13664,7 +13856,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G310" t="inlineStr"/>
@@ -13672,14 +13864,14 @@
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>novel_gene_r5</t>
+          <t>var_allele2_r1</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13687,20 +13879,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 26.9122%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 38.3853%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 34.7025%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 26.9122%; height: 42px; text-align: center;"&gt;{novelsymbol_r5}&lt;/td&gt; &lt;td style="width: 38.3853%; height: 42px; text-align: center;"&gt;{var_allele1_r5}&lt;/td&gt; &lt;td style="width: 34.7025%; height: 42px; text-align: center;"&gt;{var_allele2_r5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1'  and [method_of_diagnosis(3)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
@@ -13708,14 +13896,14 @@
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1'  and [method_of_diagnosis(3)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>enter_onset_date</t>
+          <t>var_allele1_r1</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13723,16 +13911,8 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>text</t>
@@ -13740,30 +13920,22 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>[age_onset] = '3'</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>date_dmy</t>
-        </is>
-      </c>
+          <t>[gene_type_novel] = '1'</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>(([enter_onset_date]='') AND ([diagnosis_complete]=2)) AND ([age_onset] = '3')</t>
-        </is>
-      </c>
+      <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Cannot be empty if [age_onset] = '3' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>reason_diag_other</t>
+          <t>new_novel_row2</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13771,35 +13943,23 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Other, specify:</t>
-        </is>
-      </c>
+      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>[reason_diagnosis] = '998'</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [reason_diagnosis] = '998'</t>
-        </is>
-      </c>
+      <c r="J313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>fsymptoms_other</t>
+          <t>novel_gene_r1</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13809,18 +13969,18 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Other, specify:</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; Add new row&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r1}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r1}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r1}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>[fsymptoms_id(998)] = '1'</t>
+          <t>[gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G314" t="inlineStr"/>
@@ -13828,14 +13988,14 @@
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [fsymptoms_id(998)] = '1'</t>
+          <t>If not empty, branching must be [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>neonatal_jaundice</t>
+          <t>var_allele2_r2</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13843,20 +14003,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Did the patient show neonatal jaundice?</t>
-        </is>
-      </c>
+      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>[age_onset] = '1' or [age_onset] = '2'</t>
+          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G315" t="inlineStr"/>
@@ -13864,14 +14020,14 @@
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>require_phototherapy</t>
+          <t>novelsymbol_r2</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -13879,20 +14035,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Did the patient require phototherapy?</t>
-        </is>
-      </c>
+      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>[neonatal_jaundice] = '1'</t>
+          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G316" t="inlineStr"/>
@@ -13900,14 +14052,14 @@
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [neonatal_jaundice] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>neonatal_haemolytic_anemia</t>
+          <t>var_allele1_r2</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -13915,20 +14067,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Did the patient show neonatal hemolytic anemia?</t>
-        </is>
-      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>[age_onset] = '1' or [age_onset] = '2'</t>
+          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G317" t="inlineStr"/>
@@ -13936,14 +14084,14 @@
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>requiring_blood_transfusion</t>
+          <t>new_novel_row3</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -13951,35 +14099,23 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Did the patient require blood transfusion?</t>
-        </is>
-      </c>
+      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>dropdown</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>[neonatal_haemolytic_anemia] = '1'</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [neonatal_haemolytic_anemia] = '1'</t>
-        </is>
-      </c>
+      <c r="J318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>other_neonatal</t>
+          <t>novel_gene_r2</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -13989,18 +14125,18 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Other severe complications in the neonatal period:</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r2}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r2}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r2}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row3}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>[age_onset] = '1' or [age_onset] = '2'</t>
+          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G319" t="inlineStr"/>
@@ -14008,14 +14144,14 @@
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>test_performed_12</t>
+          <t>new_novel_row4</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14023,39 +14159,23 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hemoglobin F performed </t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>dropdown</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5' or [orpha_code_id] = '13'</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5' or [orpha_code_id] = '13'</t>
-        </is>
-      </c>
+      <c r="J320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>test_performed_14</t>
+          <t>novelsymbol_r3</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14063,24 +14183,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hemoglobin A2 in diagnosis performed </t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5'</t>
+          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G321" t="inlineStr"/>
@@ -14088,14 +14200,14 @@
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5'</t>
+          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>test_result_14</t>
+          <t>var_allele1_r3</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14103,16 +14215,8 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Hemoglobin A2 in diagnosis (%)</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>text</t>
@@ -14120,26 +14224,22 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>[test_performed_14] = '1'</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
+          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_14] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>test_performed_15</t>
+          <t>var_allele2_r3</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14147,24 +14247,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abnormal Hemoglobin Fraction performed </t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '6' or [orpha_code_id] = '7' or [orpha_code_id] = '8' or [orpha_code_id] = '15' or [orpha_code_id] = '13'</t>
+          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G323" t="inlineStr"/>
@@ -14172,14 +14264,14 @@
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '6' or [orpha_code_id] = '7' or [orpha_code_id] = '8' or [orpha_code_id] = '15' or [orpha_code_id] = '13'</t>
+          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>test_performed_16</t>
+          <t>novel_gene_r3</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14189,18 +14281,18 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>p50 performed</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r3}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r3}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r3}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row4}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '8' or [sub_orpha_id_undiagnosed] = '2'</t>
+          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G324" t="inlineStr"/>
@@ -14208,14 +14300,14 @@
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '8' or [sub_orpha_id_undiagnosed] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>test_result_16</t>
+          <t>var_allele1_r4</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14223,11 +14315,7 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>p50 (mmHg)</t>
-        </is>
-      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
@@ -14236,26 +14324,22 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>([orpha_code_id] = '8' or ([orpha_code_id] = '16'  and [sub_orpha_id_undiagnosed] = '2')) and [test_performed_16] = '1'</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
+          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
-          <t>If not empty, branching must be ([orpha_code_id] = '8' or ([orpha_code_id] = '16'  and [sub_orpha_id_undiagnosed] = '2')) and [test_performed_16] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>test_performed_17</t>
+          <t>var_allele2_r4</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14263,20 +14347,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Unstable Hemoglobin test performed</t>
-        </is>
-      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '15' or [sub_orpha_id_undiagnosed] = '2'</t>
+          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G326" t="inlineStr"/>
@@ -14284,14 +14364,14 @@
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '15' or [sub_orpha_id_undiagnosed] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>test_result_17</t>
+          <t>novelsymbol_r4</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14299,20 +14379,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Unstable Hemoglobin test</t>
-        </is>
-      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>[test_performed_17] = '1'</t>
+          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G327" t="inlineStr"/>
@@ -14320,14 +14396,14 @@
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [test_performed_17] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>test_performed_31</t>
+          <t>new_novel_row5</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14335,39 +14411,23 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Pyruvate kinase performed</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>dropdown</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
-        </is>
-      </c>
+      <c r="J328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>test_result_31</t>
+          <t>novel_gene_r4</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14377,22 +14437,18 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Pyruvate kinase</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r4}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r4}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r4}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>[test_performed_31] = '1'</t>
+          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G329" t="inlineStr"/>
@@ -14400,14 +14456,14 @@
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_31] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>test_performed_32</t>
+          <t>var_allele1_r5</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14415,24 +14471,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Hexokinase performed</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
+          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G330" t="inlineStr"/>
@@ -14440,14 +14488,14 @@
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
+          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>test_result_32</t>
+          <t>var_allele2_r5</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14455,24 +14503,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Hexokinase</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>[test_performed_32] = '1'</t>
+          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="G331" t="inlineStr"/>
@@ -14480,14 +14520,14 @@
       <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_32] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>test_performed_33</t>
+          <t>novelsymbol_r5</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14495,24 +14535,16 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Glucose-6-phosphate dehydrogenase performed</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
+          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G332" t="inlineStr"/>
@@ -14520,14 +14552,14 @@
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
+          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>test_result_33</t>
+          <t>novel_gene_r5</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14537,22 +14569,18 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Glucose-6-phosphate dehydrogenase</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 26.9122%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 38.3853%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 34.7025%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 26.9122%; height: 42px; text-align: center;"&gt;{novelsymbol_r5}&lt;/td&gt; &lt;td style="width: 38.3853%; height: 42px; text-align: center;"&gt;{var_allele1_r5}&lt;/td&gt; &lt;td style="width: 34.7025%; height: 42px; text-align: center;"&gt;{var_allele2_r5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>[test_performed_33] = '1'</t>
+          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1'  and [method_of_diagnosis(3)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="G333" t="inlineStr"/>
@@ -14560,14 +14588,14 @@
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_33] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1'  and [method_of_diagnosis(3)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>test_performed_34</t>
+          <t>enter_onset_date</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14577,7 +14605,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Glucose Phosphate isomerase performed</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -14587,27 +14615,35 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '11'</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr"/>
+          <t>[age_onset] = '3'</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>date_dmy</t>
+        </is>
+      </c>
       <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>(([enter_onset_date]='') AND ([diagnosis_complete]=2)) AND ([age_onset] = '3')</t>
+        </is>
+      </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '11'</t>
+          <t>Cannot be empty if [age_onset] = '3' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>test_result_34</t>
+          <t>reason_diag_other</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14617,22 +14653,18 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Glucose Phosphate isomerase</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Other, specify:</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>[test_performed_34] = '1'</t>
+          <t>[reason_diagnosis] = '998'</t>
         </is>
       </c>
       <c r="G335" t="inlineStr"/>
@@ -14640,14 +14672,14 @@
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_34] = '1'</t>
+          <t>If not empty, branching must be [reason_diagnosis] = '998'</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>test_performed_35</t>
+          <t>fsymptoms_other</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14657,22 +14689,18 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Adenosine deaminase performed</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Other, specify:</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '18'</t>
+          <t>[fsymptoms_id(998)] = '1'</t>
         </is>
       </c>
       <c r="G336" t="inlineStr"/>
@@ -14680,14 +14708,14 @@
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '18'</t>
+          <t>If not empty, branching must be [fsymptoms_id(998)] = '1'</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>test_result_35</t>
+          <t>neonatal_jaundice</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14697,14 +14725,10 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Adenosine deaminase</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Did the patient show neonatal jaundice?</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
           <t>dropdown</t>
@@ -14712,7 +14736,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>[test_performed_35] = '1'</t>
+          <t>[age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="G337" t="inlineStr"/>
@@ -14720,14 +14744,14 @@
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_35] = '1'</t>
+          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>test_performed_36</t>
+          <t>require_phototherapy</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14737,14 +14761,10 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Adenylate kinase performed</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Did the patient require phototherapy?</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>dropdown</t>
@@ -14752,7 +14772,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '17'</t>
+          <t>[neonatal_jaundice] = '1'</t>
         </is>
       </c>
       <c r="G338" t="inlineStr"/>
@@ -14760,14 +14780,14 @@
       <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '17'</t>
+          <t>If not empty, branching must be [neonatal_jaundice] = '1'</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>test_result_36</t>
+          <t>neonatal_haemolytic_anemia</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14777,14 +14797,10 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Adenylate kinase</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Did the patient show neonatal hemolytic anemia?</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>dropdown</t>
@@ -14792,7 +14808,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>[test_performed_36] = '1'</t>
+          <t>[age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="G339" t="inlineStr"/>
@@ -14800,14 +14816,14 @@
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_36] = '1'</t>
+          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>test_performed_37</t>
+          <t>requiring_blood_transfusion</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14817,14 +14833,10 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Aldolase performed</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Did the patient require blood transfusion?</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>dropdown</t>
@@ -14832,7 +14844,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '8'</t>
+          <t>[neonatal_haemolytic_anemia] = '1'</t>
         </is>
       </c>
       <c r="G340" t="inlineStr"/>
@@ -14840,14 +14852,14 @@
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '8'</t>
+          <t>If not empty, branching must be [neonatal_haemolytic_anemia] = '1'</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>test_result_37</t>
+          <t>other_neonatal</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14857,22 +14869,18 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Aldolase</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Other severe complications in the neonatal period:</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>[test_performed_37] = '1'</t>
+          <t>[age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="G341" t="inlineStr"/>
@@ -14880,14 +14888,14 @@
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_37] = '1'</t>
+          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>test_performed_38</t>
+          <t>test_performed_12</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14897,7 +14905,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bisphosphoglycerate mutase performed</t>
+          <t xml:space="preserve">Hemoglobin F performed </t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -14912,7 +14920,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '12'</t>
+          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5' or [orpha_code_id] = '13'</t>
         </is>
       </c>
       <c r="G342" t="inlineStr"/>
@@ -14920,14 +14928,14 @@
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '12'</t>
+          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5' or [orpha_code_id] = '13'</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>test_result_38</t>
+          <t>test_performed_14</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14937,7 +14945,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bisphosphoglycerate mutase</t>
+          <t xml:space="preserve">Hemoglobin A2 in diagnosis performed </t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -14952,7 +14960,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>[test_performed_38] = '1'</t>
+          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="G343" t="inlineStr"/>
@@ -14960,14 +14968,14 @@
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_38] = '1'</t>
+          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>test_performed_39</t>
+          <t>test_result_14</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14977,7 +14985,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>NADH-cytochrome b5 reductase performed</t>
+          <t>Hemoglobin A2 in diagnosis (%)</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -14987,27 +14995,31 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '9'</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr"/>
+          <t>[test_performed_14] = '1'</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
       <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '9'</t>
+          <t>Cannot be empty if [test_performed_14] = '1'</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>test_result_39</t>
+          <t>test_performed_15</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -15017,7 +15029,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>NADH-cytochrome b5 reductase</t>
+          <t xml:space="preserve">Abnormal Hemoglobin Fraction performed </t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -15032,7 +15044,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>[test_performed_39] = '1'</t>
+          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '6' or [orpha_code_id] = '7' or [orpha_code_id] = '8' or [orpha_code_id] = '15' or [orpha_code_id] = '13'</t>
         </is>
       </c>
       <c r="G345" t="inlineStr"/>
@@ -15040,14 +15052,14 @@
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_39] = '1'</t>
+          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '6' or [orpha_code_id] = '7' or [orpha_code_id] = '8' or [orpha_code_id] = '15' or [orpha_code_id] = '13'</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>test_performed_40</t>
+          <t>test_performed_16</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -15057,14 +15069,10 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>g-Glutamylcysteine synthetase performed</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>p50 performed</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
           <t>dropdown</t>
@@ -15072,7 +15080,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '3'</t>
+          <t>[orpha_code_id] = '8' or [sub_orpha_id_undiagnosed] = '2'</t>
         </is>
       </c>
       <c r="G346" t="inlineStr"/>
@@ -15080,14 +15088,14 @@
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '3'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '8' or [sub_orpha_id_undiagnosed] = '2'</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>test_result_40</t>
+          <t>test_result_16</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -15097,37 +15105,37 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>g-Glutamylcysteine synthetase</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>p50 (mmHg)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>[test_performed_40] = '1'</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr"/>
+          <t>([orpha_code_id] = '8' or ([orpha_code_id] = '16'  and [sub_orpha_id_undiagnosed] = '2')) and [test_performed_16] = '1'</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_40] = '1'</t>
+          <t>If not empty, branching must be ([orpha_code_id] = '8' or ([orpha_code_id] = '16'  and [sub_orpha_id_undiagnosed] = '2')) and [test_performed_16] = '1'</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>test_performed_41</t>
+          <t>test_performed_17</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -15137,14 +15145,10 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Gluthathione reductase performed</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Unstable Hemoglobin test performed</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
           <t>dropdown</t>
@@ -15152,7 +15156,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '4'</t>
+          <t>[orpha_code_id] = '15' or [sub_orpha_id_undiagnosed] = '2'</t>
         </is>
       </c>
       <c r="G348" t="inlineStr"/>
@@ -15160,14 +15164,14 @@
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '4'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '15' or [sub_orpha_id_undiagnosed] = '2'</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>test_result_41</t>
+          <t>test_result_17</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -15177,14 +15181,10 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Gluthathione reductase</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>Unstable Hemoglobin test</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>dropdown</t>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>[test_performed_41] = '1'</t>
+          <t>[test_performed_17] = '1'</t>
         </is>
       </c>
       <c r="G349" t="inlineStr"/>
@@ -15200,14 +15200,14 @@
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_41] = '1'</t>
+          <t>If not empty, branching must be [test_performed_17] = '1'</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>test_performed_42</t>
+          <t>test_performed_31</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Glutathione synthetase performed</t>
+          <t>Pyruvate kinase performed</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '2'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="G350" t="inlineStr"/>
@@ -15240,14 +15240,14 @@
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '2'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>test_result_42</t>
+          <t>test_performed_32</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -15257,7 +15257,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Glutathione synthetase</t>
+          <t>Hexokinase performed</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>[test_performed_42] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="G351" t="inlineStr"/>
@@ -15280,14 +15280,14 @@
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_42] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>test_performed_43</t>
+          <t>test_performed_33</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Phosphofructokinase performed</t>
+          <t>Glucose-6-phosphate dehydrogenase performed</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '6'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="G352" t="inlineStr"/>
@@ -15320,14 +15320,14 @@
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '6'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>test_result_43</t>
+          <t>test_performed_34</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Phosphofructokinase</t>
+          <t>Glucose Phosphate isomerase performed</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>[test_performed_43] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '11'</t>
         </is>
       </c>
       <c r="G353" t="inlineStr"/>
@@ -15360,14 +15360,14 @@
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_43] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '11'</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>test_performed_44</t>
+          <t>test_performed_35</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Phosphoglycerate kinase performed</t>
+          <t>Adenosine deaminase performed</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '9'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '18'</t>
         </is>
       </c>
       <c r="G354" t="inlineStr"/>
@@ -15400,14 +15400,14 @@
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '9'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '18'</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>test_result_44</t>
+          <t>test_performed_36</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Phosphoglycerate kinase</t>
+          <t>Adenylate kinase performed</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>[test_performed_44] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '17'</t>
         </is>
       </c>
       <c r="G355" t="inlineStr"/>
@@ -15440,14 +15440,14 @@
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_44] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '17'</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>test_performed_45</t>
+          <t>test_performed_37</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Pyrimidine-5'-nucleotidase performed</t>
+          <t>Aldolase performed</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '16'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '8'</t>
         </is>
       </c>
       <c r="G356" t="inlineStr"/>
@@ -15480,14 +15480,14 @@
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '16'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '8'</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>test_result_45</t>
+          <t>test_performed_38</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Pyrimidine-5'-nucleotidase</t>
+          <t>Bisphosphoglycerate mutase performed</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>[test_performed_45] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '12'</t>
         </is>
       </c>
       <c r="G357" t="inlineStr"/>
@@ -15520,14 +15520,14 @@
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_45] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '12'</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>test_performed_46</t>
+          <t>test_performed_39</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Triosephosphate isomerase performed</t>
+          <t>NADH-cytochrome b5 reductase performed</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '7'</t>
+          <t>[orpha_code_id] = '9'</t>
         </is>
       </c>
       <c r="G358" t="inlineStr"/>
@@ -15560,14 +15560,14 @@
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '7'</t>
+          <t>Cannot be empty if [orpha_code_id] = '9'</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>test_result_46</t>
+          <t>test_performed_40</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Triosephosphate isomerase</t>
+          <t>g-Glutamylcysteine synthetase performed</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>[test_performed_46] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '3'</t>
         </is>
       </c>
       <c r="G359" t="inlineStr"/>
@@ -15600,14 +15600,14 @@
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_46] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '3'</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>test_performed_47</t>
+          <t>test_performed_41</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Eosin-5-maleimide (EMA) binding test performed</t>
+          <t>Gluthathione reductase performed</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '4'</t>
         </is>
       </c>
       <c r="G360" t="inlineStr"/>
@@ -15640,14 +15640,14 @@
       <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '4'</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>test_result_47</t>
+          <t>test_performed_42</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Eosin-5-maleimide (EMA) binding test</t>
+          <t>Glutathione synthetase performed</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>[test_performed_47] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '2'</t>
         </is>
       </c>
       <c r="G361" t="inlineStr"/>
@@ -15680,14 +15680,14 @@
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_47] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '2'</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>test_performed_48</t>
+          <t>test_performed_43</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Ektacytometry performed</t>
+          <t>Phosphofructokinase performed</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '6'</t>
         </is>
       </c>
       <c r="G362" t="inlineStr"/>
@@ -15720,14 +15720,14 @@
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '6'</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>test_result_48</t>
+          <t>test_performed_44</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ektacytometry</t>
+          <t>Phosphoglycerate kinase performed</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>[test_performed_48] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '9'</t>
         </is>
       </c>
       <c r="G363" t="inlineStr"/>
@@ -15760,14 +15760,14 @@
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_48] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '9'</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>test_result_48_other</t>
+          <t>test_performed_45</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other, specify </t>
+          <t>Pyrimidine-5'-nucleotidase performed</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>[test_result_48] = '8'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '16'</t>
         </is>
       </c>
       <c r="G364" t="inlineStr"/>
@@ -15800,14 +15800,14 @@
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_result_48] = '8'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '16'</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>test_performed_49</t>
+          <t>test_performed_46</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Sodium dodecyl sulfate-polyacrylamide gel electrophoresis (SDS-PAGE)  performed</t>
+          <t>Triosephosphate isomerase performed</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '7'</t>
         </is>
       </c>
       <c r="G365" t="inlineStr"/>
@@ -15840,14 +15840,14 @@
       <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '7'</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>test_result_49</t>
+          <t>test_performed_47</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -15857,7 +15857,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sodium dodecyl sulfate-polyacrylamide gel electrophoresis (SDS-PAGE) </t>
+          <t>Eosin-5-maleimide (EMA) binding test performed</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>[test_performed_49] = '1'</t>
+          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="G366" t="inlineStr"/>
@@ -15880,14 +15880,14 @@
       <c r="I366" t="inlineStr"/>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_49] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>test_result_49_other</t>
+          <t>test_performed_48</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other, specify </t>
+          <t>Ektacytometry performed</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -15907,12 +15907,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>[test_result_49] = '8'</t>
+          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="G367" t="inlineStr"/>
@@ -15920,14 +15920,14 @@
       <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_result_49] = '8'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>test_performed_50</t>
+          <t>test_result_48_other</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Osmotic Fragility Test or glycerol lysis test performed</t>
+          <t xml:space="preserve">Other, specify </t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -15947,12 +15947,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
+          <t>[test_result_48] = '8'</t>
         </is>
       </c>
       <c r="G368" t="inlineStr"/>
@@ -15960,14 +15960,14 @@
       <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [test_result_48] = '8'</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>test_result_50</t>
+          <t>test_performed_49</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Osmotic Fragility Test or glycerol lysis test</t>
+          <t>Sodium dodecyl sulfate-polyacrylamide gel electrophoresis (SDS-PAGE)  performed</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>[test_performed_50] = '1'</t>
+          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="G369" t="inlineStr"/>
@@ -16000,14 +16000,14 @@
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_50] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>test_performed_51</t>
+          <t>test_result_49_other</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Hepcidin performed</t>
+          <t xml:space="preserve">Other, specify </t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -16027,12 +16027,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '14' or [orpha_code_id] = '3'</t>
+          <t>[test_result_49] = '8'</t>
         </is>
       </c>
       <c r="G370" t="inlineStr"/>
@@ -16040,14 +16040,14 @@
       <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '14' or [orpha_code_id] = '3'</t>
+          <t>Cannot be empty if [test_result_49] = '8'</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>test_result_51</t>
+          <t>test_performed_50</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Hepcidin</t>
+          <t>Osmotic Fragility Test or glycerol lysis test performed</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>[test_performed_51] = '1'</t>
+          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="G371" t="inlineStr"/>
@@ -16080,14 +16080,14 @@
       <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_51] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>test_performed_52</t>
+          <t>test_performed_51</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Bone marrow examination performed</t>
+          <t>Hepcidin performed</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '14' or [orpha_code_id] = '3' or [orpha_code_id] = '5'</t>
+          <t>[orpha_code_id] = '14' or [orpha_code_id] = '3'</t>
         </is>
       </c>
       <c r="G372" t="inlineStr"/>
@@ -16120,14 +16120,14 @@
       <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '14' or [orpha_code_id] = '3' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [orpha_code_id] = '14' or [orpha_code_id] = '3'</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>test_result_52</t>
+          <t>test_performed_52</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Bone marrow examination</t>
+          <t>Bone marrow examination performed</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -16147,12 +16147,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>[test_performed_52] = '1'</t>
+          <t>[orpha_code_id] = '14' or [orpha_code_id] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="G373" t="inlineStr"/>
@@ -16160,7 +16160,7 @@
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_52] = '1'</t>
+          <t>Cannot be empty if [orpha_code_id] = '14' or [orpha_code_id] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
     </row>
@@ -19380,7 +19380,7 @@
       <c r="I466" t="inlineStr"/>
       <c r="J466" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications] = '1' / If [acute_id_r1] = '9' or [acute_id_r1] = '18' or [acute_id_r1] = '20' or [acute_id_r1] = '22', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       <c r="I473" t="inlineStr"/>
       <c r="J473" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications] = '1' / If [acute_id_r2] = '9' or [acute_id_r2] = '18' or [acute_id_r2] = '20' or [acute_id_r2] = '22', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -19904,7 +19904,7 @@
       <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications] = '1' / If [acute_id_r3] = '9' or [acute_id_r3] = '18' or [acute_id_r3] = '20' or [acute_id_r3] = '22', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -20164,7 +20164,7 @@
       <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications] = '1' / If [acute_id_r4] = '9' or [acute_id_r4] = '18' or [acute_id_r4] = '20' or [acute_id_r4] = '22', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -20540,7 +20540,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r2] = '25' or [acute_id_scd_r2] = '27' or [acute_id_scd_r2] = '35' or [acute_id_scd_r2] = '42', or [acute_id_scd_r2] = '44', or [acute_id_scd_r2] = '45', or [acute_id_scd_r2] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -20812,7 +20812,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r3] = '25' or [acute_id_scd_r3] = '27' or [acute_id_scd_r3] = '35' or [acute_id_scd_r3] = '42', or [acute_id_scd_r3] = '44', or [acute_id_scd_r3] = '45', or [acute_id_scd_r3] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r4] = '25' or [acute_id_scd_r4] = '27' or [acute_id_scd_r4] = '35' or [acute_id_scd_r4] = '42', or [acute_id_scd_r4] = '44', or [acute_id_scd_r4] = '45', or [acute_id_scd_r4] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -21356,7 +21356,7 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r5] = '25' or [acute_id_scd_r5] = '27' or [acute_id_scd_r5] = '35' or [acute_id_scd_r5] = '42', or [acute_id_scd_r5] = '44', or [acute_id_scd_r5] = '45', or [acute_id_scd_r5] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -21628,7 +21628,7 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r6] = '25' or [acute_id_scd_r6] = '27' or [acute_id_scd_r6] = '35' or [acute_id_scd_r6] = '42', or [acute_id_scd_r6] = '44', or [acute_id_scd_r6] = '45', or [acute_id_scd_r6] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -21900,7 +21900,7 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r7] = '25' or [acute_id_scd_r7] = '27' or [acute_id_scd_r7] = '35' or [acute_id_scd_r7] = '42', or [acute_id_scd_r7] = '44', or [acute_id_scd_r7] = '45', or [acute_id_scd_r7] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -22174,7 +22174,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r8] = '25' or [acute_id_scd_r8] = '27' or [acute_id_scd_r8] = '35' or [acute_id_scd_r8] = '42', or [acute_id_scd_r8] = '44', or [acute_id_scd_r8] = '45', or [acute_id_scd_r8] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r9] = '25' or [acute_id_scd_r9] = '27' or [acute_id_scd_r9] = '35' or [acute_id_scd_r9] = '42', or [acute_id_scd_r9] = '44', or [acute_id_scd_r9] = '45', or [acute_id_scd_r9] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -22720,7 +22720,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r10] = '25' or [acute_id_scd_r10] = '27' or [acute_id_scd_r10] = '35' or [acute_id_scd_r10] = '42', or [acute_id_scd_r10] = '44', or [acute_id_scd_r10] = '45', or [acute_id_scd_r10] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -22992,7 +22992,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r11] = '25' or [acute_id_scd_r11] = '27' or [acute_id_scd_r11] = '35' or [acute_id_scd_r11] = '42', or [acute_id_scd_r11] = '44', or [acute_id_scd_r11] = '45', or [acute_id_scd_r11] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -23264,7 +23264,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r12] = '25' or [acute_id_scd_r12] = '27' or [acute_id_scd_r12] = '35' or [acute_id_scd_r12] = '42', or [acute_id_scd_r12] = '44', or [acute_id_scd_r12] = '45', or [acute_id_scd_r12] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r13] = '25' or [acute_id_scd_r13] = '27' or [acute_id_scd_r13] = '35' or [acute_id_scd_r13] = '42', or [acute_id_scd_r13] = '44', or [acute_id_scd_r13] = '45', or [acute_id_scd_r13] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r14] = '25' or [acute_id_scd_r14] = '27' or [acute_id_scd_r14] = '35' or [acute_id_scd_r14] = '42', or [acute_id_scd_r14] = '44', or [acute_id_scd_r14] = '45', or [acute_id_scd_r14] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -24080,7 +24080,7 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r15] = '25' or [acute_id_scd_r15] = '27' or [acute_id_scd_r15] = '35' or [acute_id_scd_r15] = '42', or [acute_id_scd_r15] = '44', or [acute_id_scd_r15] = '45', or [acute_id_scd_r15] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
@@ -24352,7 +24352,7 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r16] = '25' or [acute_id_scd_r16] = '27' or [acute_id_scd_r16] = '35' or [acute_id_scd_r16] = '42', or [acute_id_scd_r16] = '44', or [acute_id_scd_r16] = '45', or [acute_id_scd_r16] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
     </row>
